--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9626,7 +9626,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9676,7 +9676,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9726,7 +9726,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9776,7 +9776,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9826,7 +9826,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9876,7 +9876,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9926,7 +9926,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Story Phase</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Image Prompt</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Caption Context</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Next Day Teaser</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Mood</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hashtags</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -4876,7 +4864,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5214,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7564,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9914,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Story Phase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Image Prompt</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Caption Context</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Next Day Teaser</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Mood</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hashtags</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -4864,7 +4876,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -5226,7 +5226,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -7576,7 +7576,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9926,7 +9926,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -9976,7 +9976,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10026,7 +10026,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10076,7 +10076,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10126,7 +10126,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10176,7 +10176,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10226,7 +10226,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10276,7 +10276,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10326,7 +10326,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10376,7 +10376,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10426,7 +10426,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10476,7 +10476,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10526,7 +10526,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10576,7 +10576,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10626,7 +10626,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10676,7 +10676,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10726,7 +10726,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10776,7 +10776,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10826,7 +10826,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10876,7 +10876,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10926,7 +10926,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -10976,7 +10976,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11026,7 +11026,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11076,7 +11076,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11126,7 +11126,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11176,7 +11176,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11226,7 +11226,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11276,7 +11276,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11326,7 +11326,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11376,7 +11376,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11426,7 +11426,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11476,7 +11476,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11526,7 +11526,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11576,7 +11576,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11626,7 +11626,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11676,7 +11676,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11726,7 +11726,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Story Phase</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Image Prompt</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Caption Context</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Next Day Teaser</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Mood</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hashtags</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -11626,7 +11614,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11714,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Story Phase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Image Prompt</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Caption Context</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Next Day Teaser</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Mood</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hashtags</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -11614,7 +11626,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11726,7 +11726,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11776,7 +11776,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Story Phase</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Image Prompt</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Caption Context</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Next Day Teaser</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Mood</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hashtags</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -11776,7 +11764,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Story Phase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Image Prompt</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Caption Context</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Next Day Teaser</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Style</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Mood</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hashtags</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -11764,7 +11776,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11826,7 +11826,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Posted</t>
         </is>
       </c>
     </row>

--- a/data/story.xlsx
+++ b/data/story.xlsx
@@ -11876,7 +11876,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
